--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="أسبوع_9" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="أسبوع_10" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="أسبوع_10" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,20 +459,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الأربعاء</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45718</v>
+        <v>45728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23:30:55</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>23:30:57</t>
+          <t>23:34:50</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -483,25 +477,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>محمد مفيد</t>
+          <t>ندى</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الأربعاء</t>
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45718</v>
+        <v>45728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23:31:02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>23:31:06</t>
+          <t>23:34:53</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -511,29 +500,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>محمد مراد</t>
+          <t>مرح</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الأربعاء</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45718</v>
+        <v>45728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23:31:54</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>23:34:40</t>
+          <t>23:34:57</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -544,24 +528,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الأربعاء</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45718</v>
+        <v>45728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23:31:43</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>23:35:04</t>
+          <t>23:41:11</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -572,24 +551,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الأربعاء</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45718</v>
+        <v>45728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23:31:36</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>23:35:13</t>
+          <t>23:41:16</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -600,209 +574,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الأربعاء</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45718</v>
+        <v>45728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23:31:49</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>23:35:17</t>
+          <t>23:41:19</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>اسم الموظف</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>اليوم</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>تاريخ</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>وقت الدخول</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>وقت الخروج</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ساعات العمل</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ندى</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>محمد مراد</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>الأربعاء</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C8" s="1" t="n">
         <v>45728</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>22:36:14</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>22:36:56</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>محمد مراد</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>الأربعاء</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>45728</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>22:36:04</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>22:45:12</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> مازن</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>الأربعاء</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>45728</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>22:36:08</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>22:45:17</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>محمد ممدوح</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>الأربعاء</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>45728</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>22:36:11</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>22:45:22</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>محمد مفيد</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>الأربعاء</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>45728</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>22:45:37</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>22:45:53</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>23:44:12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
         <v>0</v>
       </c>
     </row>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,8 +608,35 @@
           <t>23:44:12</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>محمد مراد</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>23:44:12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>23:44:19</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,6 +640,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>محمد مراد</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>23:45:07</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,8 +659,31 @@
           <t>23:45:07</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>محمد مراد</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>23:45:27</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,8 +682,35 @@
           <t>23:45:27</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>محمد مراد</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>23:45:27</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>23:45:34</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,6 +714,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>محمد مفيد</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>23:45:39</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,8 +733,35 @@
           <t>23:45:39</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>محمد مفيد</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>23:45:39</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>23:45:44</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,6 +765,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>مرح</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>23:57:09</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -784,7 +784,6 @@
           <t>23:57:09</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>0</v>
       </c>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>مرح</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>23:58:03</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,8 +807,31 @@
           <t>23:58:03</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>محمد ممدوح</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>23:58:08</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
         <v>0</v>
       </c>
     </row>

--- a/G:\app\سجل_العمل.xlsx
+++ b/G:\app\سجل_العمل.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,8 +830,31 @@
           <t>23:58:08</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>محمد مراد</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>الأربعاء</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>23:58:13</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
         <v>0</v>
       </c>
     </row>
